--- a/results/MVSE/freebase/MVSE_freebase<l05>AllRes_62.32.xlsx
+++ b/results/MVSE/freebase/MVSE_freebase<l05>AllRes_62.32.xlsx
@@ -522,7 +522,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
